--- a/data/satisfaction_detail/2026/1-8月/参会人员.xlsx
+++ b/data/satisfaction_detail/2026/1-8月/参会人员.xlsx
@@ -472,10 +472,10 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>9.779999999999999</v>
+        <v>9.78597962756645</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>9.960000000000001</v>
+        <v>9.949794153535997</v>
       </c>
     </row>
     <row r="3">
@@ -485,10 +485,10 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>9.99</v>
+        <v>9.991858984561516</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>10</v>
+        <v>9.998511857392964</v>
       </c>
     </row>
     <row r="4">
@@ -501,7 +501,7 @@
         <v>10</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>10</v>
+        <v>9.99702371478593</v>
       </c>
     </row>
     <row r="5">
@@ -537,10 +537,10 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>10</v>
+        <v>9.999999999999998</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>10</v>
+        <v>9.999999999999998</v>
       </c>
     </row>
     <row r="8">
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>9.960000000000001</v>
+        <v>9.962828266751552</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>10</v>
+        <v>9.998511857392964</v>
       </c>
     </row>
     <row r="9">
@@ -563,10 +563,10 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>9.550000000000001</v>
+        <v>9.545510106636957</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>9.890000000000001</v>
+        <v>9.877359541620244</v>
       </c>
     </row>
     <row r="10">
@@ -576,10 +576,10 @@
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>9.65</v>
+        <v>9.634285107963288</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>9.92</v>
+        <v>9.909993633614516</v>
       </c>
     </row>
     <row r="11">
@@ -589,10 +589,10 @@
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>9.279999999999999</v>
+        <v>9.289248766512813</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>9.85</v>
+        <v>9.845513289829698</v>
       </c>
     </row>
     <row r="12">
@@ -602,10 +602,10 @@
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>9.42</v>
+        <v>9.416338267282084</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>9.880000000000001</v>
+        <v>9.86155870337949</v>
       </c>
     </row>
     <row r="13">
@@ -615,10 +615,10 @@
         </is>
       </c>
       <c r="B13" s="4" t="n">
-        <v>9.51</v>
+        <v>9.509374502626134</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>9.869999999999999</v>
+        <v>9.854617221072736</v>
       </c>
     </row>
     <row r="14">
@@ -628,10 +628,10 @@
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>9.81</v>
+        <v>9.801321024988065</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>9.890000000000001</v>
+        <v>9.878357472544964</v>
       </c>
     </row>
     <row r="15">
@@ -641,10 +641,10 @@
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>8.869999999999999</v>
+        <v>8.855425752029285</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>9.720000000000001</v>
+        <v>9.715863971563477</v>
       </c>
     </row>
     <row r="16">
@@ -654,10 +654,10 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>9.92</v>
+        <v>9.913150299750651</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>9.960000000000001</v>
+        <v>9.954550374025146</v>
       </c>
     </row>
     <row r="17">
@@ -667,10 +667,10 @@
         </is>
       </c>
       <c r="B17" s="4" t="n">
-        <v>9.949999999999999</v>
+        <v>9.951196349938989</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>9.99</v>
+        <v>9.983227757440714</v>
       </c>
     </row>
     <row r="18">
@@ -680,10 +680,10 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>9.81</v>
+        <v>9.822726404583799</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>9.99</v>
+        <v>9.972384741896121</v>
       </c>
     </row>
     <row r="19">
@@ -693,10 +693,10 @@
         </is>
       </c>
       <c r="B19" s="4" t="n">
-        <v>9.380000000000001</v>
+        <v>9.482683431481776</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>9.970000000000001</v>
+        <v>9.931206960581463</v>
       </c>
     </row>
     <row r="20">
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="B20" s="4" t="n">
-        <v>9.84</v>
+        <v>9.789514509272379</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>9.99</v>
+        <v>9.954165207703326</v>
       </c>
     </row>
     <row r="21">
